--- a/public/templates/GiziBalita.xlsx
+++ b/public/templates/GiziBalita.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27932"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29426"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0dccc67157c6ef23/文档/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PROJECT WEB RANDIKA\sipandakabulan-new\public\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{62C16DAB-393F-478F-8EA8-C4C2CEF21AC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{536E7972-22A0-4432-893E-0857A1CB3B1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{D86A2EEE-D591-4AC3-9D84-3D0D4BC1E4F5}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{D86A2EEE-D591-4AC3-9D84-3D0D4BC1E4F5}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,8 +27,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -699,9 +697,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC753C9B-C72C-4A52-890F-35DB00672DA5}">
   <dimension ref="B4:L9"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="4" spans="2:12" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B4" s="12" t="s">
         <v>0</v>
       </c>
@@ -714,15 +712,15 @@
       <c r="G4" s="14"/>
       <c r="H4" s="15"/>
       <c r="I4" s="19">
-        <v>2021</v>
+        <v>2024</v>
       </c>
       <c r="J4" s="20"/>
       <c r="K4" s="19">
-        <v>2022</v>
+        <v>2025</v>
       </c>
       <c r="L4" s="20"/>
     </row>
-    <row r="5" spans="2:12" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B5" s="12"/>
       <c r="C5" s="16"/>
       <c r="D5" s="17"/>
@@ -743,7 +741,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="2:12" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B6" s="3">
         <v>1</v>
       </c>
@@ -760,7 +758,7 @@
       <c r="K6" s="5"/>
       <c r="L6" s="5"/>
     </row>
-    <row r="7" spans="2:12" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B7" s="2"/>
       <c r="C7" s="6" t="s">
         <v>5</v>
@@ -775,7 +773,7 @@
       <c r="K7" s="5"/>
       <c r="L7" s="5"/>
     </row>
-    <row r="8" spans="2:12" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B8" s="2"/>
       <c r="C8" s="9" t="s">
         <v>6</v>
@@ -790,7 +788,7 @@
       <c r="K8" s="5"/>
       <c r="L8" s="5"/>
     </row>
-    <row r="9" spans="2:12" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B9" s="2"/>
       <c r="C9" s="9" t="s">
         <v>7</v>
@@ -807,14 +805,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="C6:H6"/>
     <mergeCell ref="C7:H7"/>
     <mergeCell ref="C8:H8"/>
     <mergeCell ref="C9:H9"/>
     <mergeCell ref="B4:B5"/>
     <mergeCell ref="C4:H5"/>
-    <mergeCell ref="I4:J4"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="C6:H6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
